--- a/static/docs/excel_temporal.xlsx
+++ b/static/docs/excel_temporal.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -458,37 +458,25 @@
           <t>Mes Inicial</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Mayo</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>2024</v>
-      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Mes Final</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Septiembre</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>2024</v>
-      </c>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -498,7 +486,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>CASTELLANOS LEAL ANGEL ALFONSO - 11258909 - 3851</t>
+          <t>CABRERA RUIZ INES MARIA - 30898144 - 12062</t>
         </is>
       </c>
     </row>
@@ -531,7 +519,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>1</v>
+        <v>575</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -539,18 +527,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>270000</v>
+        <v>3501811</v>
       </c>
       <c r="F9" t="n">
-        <v>3851</v>
+        <v>12062</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>2</v>
+        <v>576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -558,470 +546,344 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>32400</v>
+        <v>498192</v>
       </c>
       <c r="F10" t="n">
-        <v>3851</v>
+        <v>12062</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>15</v>
+        <v>589</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Auxilio de Rodamiento</t>
+          <t>Intereses de Cesantias</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E11" t="n">
-        <v>60000</v>
+        <v>33823</v>
       </c>
       <c r="F11" t="n">
-        <v>3851</v>
+        <v>12062</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>20</v>
+        <v>590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cesantias</t>
+          <t xml:space="preserve">Fondo Cesantias </t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="E12" t="n">
-        <v>470400</v>
+        <v>676458</v>
       </c>
       <c r="F12" t="n">
-        <v>3851</v>
+        <v>12062</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>21</v>
+        <v>617</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Intereses de Cesantias</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>17562</v>
+        <v>-140072</v>
       </c>
       <c r="F13" t="n">
-        <v>3851</v>
+        <v>12062</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>23</v>
+        <v>618</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prima de Servicios</t>
+          <t>AFP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>470400</v>
+        <v>-140072</v>
       </c>
       <c r="F14" t="n">
-        <v>3851</v>
+        <v>12062</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>32</v>
+        <v>629</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Cesantias Consolidadas</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.7</v>
+        <v>150</v>
       </c>
       <c r="E15" t="n">
-        <v>210150</v>
+        <v>676458</v>
       </c>
       <c r="F15" t="n">
-        <v>3851</v>
+        <v>12062</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
+        <v>630</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Intereses Consolidados</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>150</v>
+      </c>
+      <c r="E16" t="n">
+        <v>33823</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12062</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5140421</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>CABRERA VEGA YARELIS ESTHER - 32941504 - 12063</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>575</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>60</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-10800</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3851</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="n">
-        <v>70</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AFP</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-10800</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3851</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1509312</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Empleado</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>DIAZ DIAZ MIGUEL ANGEL  - 1075629124 - 3781</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Id Concepto</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Nombre Concepto</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Contrato</t>
-        </is>
+      <c r="E21" t="n">
+        <v>3501811</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12063</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>1</v>
+        <v>576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sueldo Basico</t>
+          <t>Auxilio de Transporte</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>96666</v>
+        <v>498192</v>
       </c>
       <c r="F22" t="n">
-        <v>3781</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
-        <v>2</v>
+        <v>589</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auxilio de Transporte</t>
+          <t>Intereses de Cesantias</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="E23" t="n">
-        <v>10800</v>
+        <v>33823</v>
       </c>
       <c r="F23" t="n">
-        <v>3781</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>15</v>
+        <v>590</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Auxilio de Rodamiento</t>
+          <t xml:space="preserve">Fondo Cesantias </t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E24" t="n">
-        <v>60000</v>
+        <v>676458</v>
       </c>
       <c r="F24" t="n">
-        <v>3781</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>20</v>
+        <v>617</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cesantias</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>483600</v>
+        <v>-140072</v>
       </c>
       <c r="F25" t="n">
-        <v>3781</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>21</v>
+        <v>618</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Intereses de Cesantias</t>
+          <t>AFP</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>17410</v>
+        <v>-140072</v>
       </c>
       <c r="F26" t="n">
-        <v>3781</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>23</v>
+        <v>629</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prima de Servicios</t>
+          <t>Cesantias Consolidadas</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="E27" t="n">
-        <v>483600</v>
+        <v>676458</v>
       </c>
       <c r="F27" t="n">
-        <v>3781</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>32</v>
+        <v>630</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Intereses Consolidados</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.5</v>
+        <v>150</v>
       </c>
       <c r="E28" t="n">
-        <v>217500</v>
+        <v>33823</v>
       </c>
       <c r="F28" t="n">
-        <v>3781</v>
+        <v>12063</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>60</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-3867</v>
-      </c>
-      <c r="F29" t="n">
-        <v>3781</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>70</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AFP</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-3867</v>
-      </c>
-      <c r="F30" t="n">
-        <v>3781</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="n">
-        <v>94</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Dsct. Autorizado Herramienta</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-76000</v>
-      </c>
-      <c r="F31" t="n">
-        <v>3781</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1285842</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Empleado</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>OVALLE RIAÑO JAVIER None - 79845008 - 2397</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Id Concepto</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Nombre Concepto</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Contrato</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="n">
-        <v>32</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Vacaciones Compensadas</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>15</v>
-      </c>
-      <c r="E36" t="n">
-        <v>3134000</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2397</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>3134000</v>
+      <c r="C29" t="n">
+        <v>5140421</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C20:H20"/>
+  <mergeCells count="3">
+    <mergeCell ref="C19:H19"/>
     <mergeCell ref="C7:H7"/>
-    <mergeCell ref="C34:H34"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/static/docs/excel_temporal.xlsx
+++ b/static/docs/excel_temporal.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>CABRERA RUIZ INES MARIA - 30898144 - 12062</t>
+          <t>QUINTERO GUTIERREZ WILLIAM - 19483492 - 12080</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>575</v>
+        <v>510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -527,18 +527,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>3501811</v>
+        <v>4956733</v>
       </c>
       <c r="F9" t="n">
-        <v>12062</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>576</v>
+        <v>511</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -546,345 +546,7716 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>498192</v>
+        <v>489887</v>
       </c>
       <c r="F10" t="n">
-        <v>12062</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>589</v>
+        <v>520</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Intereses de Cesantias</t>
+          <t>Auxilio de Rodamiento</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>33823</v>
+        <v>1820000</v>
       </c>
       <c r="F11" t="n">
-        <v>12062</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>590</v>
+        <v>552</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo Cesantias </t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>676458</v>
+        <v>-198269</v>
       </c>
       <c r="F12" t="n">
-        <v>12062</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>617</v>
+        <v>553</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>AFP</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-198269</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12080</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6870082</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>HERNANDEZ FIGUEREDO EDINSON - 80138563 - 12081</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>510</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>59</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4147293</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12081</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>511</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>59</v>
+      </c>
+      <c r="E19" t="n">
+        <v>489888</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12081</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>520</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>-140072</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12062</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="n">
-        <v>618</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AFP</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-140072</v>
-      </c>
-      <c r="F14" t="n">
-        <v>12062</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="n">
-        <v>629</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Cesantias Consolidadas</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>150</v>
-      </c>
-      <c r="E15" t="n">
-        <v>676458</v>
-      </c>
-      <c r="F15" t="n">
-        <v>12062</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="n">
-        <v>630</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Intereses Consolidados</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>150</v>
-      </c>
-      <c r="E16" t="n">
-        <v>33823</v>
-      </c>
-      <c r="F16" t="n">
-        <v>12062</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>5140421</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Empleado</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>CABRERA VEGA YARELIS ESTHER - 32941504 - 12063</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Id Concepto</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Nombre Concepto</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Contrato</t>
-        </is>
+      <c r="E20" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12081</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sueldo Basico</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>3501811</v>
+        <v>-165892</v>
       </c>
       <c r="F21" t="n">
-        <v>12063</v>
+        <v>12081</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>576</v>
+        <v>553</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Auxilio de Transporte</t>
+          <t>AFP</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>498192</v>
+        <v>-165892</v>
       </c>
       <c r="F22" t="n">
-        <v>12063</v>
+        <v>12081</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>589</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Intereses de Cesantias</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>150</v>
-      </c>
-      <c r="E23" t="n">
-        <v>33823</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12063</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="n">
-        <v>590</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fondo Cesantias </t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>150</v>
-      </c>
-      <c r="E24" t="n">
-        <v>676458</v>
-      </c>
-      <c r="F24" t="n">
-        <v>12063</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7505397</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>617</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-140072</v>
-      </c>
-      <c r="F25" t="n">
-        <v>12063</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ZAPATA PAEZ YARITZA AMANDA - 1022402087 - 12083</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>618</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AFP</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-140072</v>
-      </c>
-      <c r="F26" t="n">
-        <v>12063</v>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
-        <v>629</v>
+        <v>510</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cesantias Consolidadas</t>
+          <t>Sueldo Basico</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
-        <v>676458</v>
+        <v>3151631</v>
       </c>
       <c r="F27" t="n">
-        <v>12063</v>
+        <v>12083</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>630</v>
+        <v>511</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Intereses Consolidados</t>
+          <t>Auxilio de Transporte</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>33823</v>
+        <v>448373</v>
       </c>
       <c r="F28" t="n">
-        <v>12063</v>
+        <v>12083</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" t="n">
+        <v>520</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12083</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>552</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-137738</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12083</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>553</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-137738</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12083</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>5140421</v>
+      <c r="C32" t="n">
+        <v>3374528</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>LOPEZ SUSA GERALDIN - 1065917402 - 12084</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>510</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3443448</v>
+      </c>
+      <c r="F36" t="n">
+        <v>12084</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>511</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>59</v>
+      </c>
+      <c r="E37" t="n">
+        <v>489888</v>
+      </c>
+      <c r="F37" t="n">
+        <v>12084</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>520</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>12084</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>552</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-137738</v>
+      </c>
+      <c r="F39" t="n">
+        <v>12084</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>553</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-137738</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12084</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4057860</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>LOZANO ARANGO RUBY PAOLA - 52824603 - 12087</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>510</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>56</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3522618</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12087</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>511</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>56</v>
+      </c>
+      <c r="E46" t="n">
+        <v>464979</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12087</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>520</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>344335</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12087</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>552</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-140904</v>
+      </c>
+      <c r="F48" t="n">
+        <v>12087</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>553</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-140904</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12087</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4050124</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>NIÑO AVELLA JUAN CARLOS - 74182544 - 12088</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>510</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>56</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3345952</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12088</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>511</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>56</v>
+      </c>
+      <c r="E55" t="n">
+        <v>464978</v>
+      </c>
+      <c r="F55" t="n">
+        <v>12088</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>520</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1324867</v>
+      </c>
+      <c r="F56" t="n">
+        <v>12088</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>552</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F57" t="n">
+        <v>12088</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>553</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F58" t="n">
+        <v>12088</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4868121</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>OROZCO NIÑO HECTOR JAVIER - 74344897 - 12089</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>510</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>53</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3170861</v>
+      </c>
+      <c r="F63" t="n">
+        <v>12089</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>511</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>53</v>
+      </c>
+      <c r="E64" t="n">
+        <v>440068</v>
+      </c>
+      <c r="F64" t="n">
+        <v>12089</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>520</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1254858</v>
+      </c>
+      <c r="F65" t="n">
+        <v>12089</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>527</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Incapacidad E.Gral</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>58364</v>
+      </c>
+      <c r="F66" t="n">
+        <v>12089</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>528</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Incapacidad 2 dias E.Gral.</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>116727</v>
+      </c>
+      <c r="F67" t="n">
+        <v>12089</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>552</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F68" t="n">
+        <v>12089</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>553</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F69" t="n">
+        <v>12089</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4773202</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ MENDOZA CESAR HERNANDO - 79663392 - 12090</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>510</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>56</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3345952</v>
+      </c>
+      <c r="F74" t="n">
+        <v>12090</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>511</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>56</v>
+      </c>
+      <c r="E75" t="n">
+        <v>464978</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12090</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>520</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1324867</v>
+      </c>
+      <c r="F76" t="n">
+        <v>12090</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>552</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F77" t="n">
+        <v>12090</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>553</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F78" t="n">
+        <v>12090</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>4868121</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>ARIZA RODRIGUEZ GUADALUPE - 80127485 - 12093</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>510</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>56</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3449858</v>
+      </c>
+      <c r="F83" t="n">
+        <v>12093</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>511</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>56</v>
+      </c>
+      <c r="E84" t="n">
+        <v>464979</v>
+      </c>
+      <c r="F84" t="n">
+        <v>12093</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>520</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2344667</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12093</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>552</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>4</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-137994</v>
+      </c>
+      <c r="F86" t="n">
+        <v>12093</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>553</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-137994</v>
+      </c>
+      <c r="F87" t="n">
+        <v>12093</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5983516</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>BERNAL GOMEZ SONIA MILENA - 1013633592 - 12094</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>510</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>56</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3268358</v>
+      </c>
+      <c r="F92" t="n">
+        <v>12094</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>511</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>56</v>
+      </c>
+      <c r="E93" t="n">
+        <v>464979</v>
+      </c>
+      <c r="F93" t="n">
+        <v>12094</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>520</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F94" t="n">
+        <v>12094</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>552</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-130734</v>
+      </c>
+      <c r="F95" t="n">
+        <v>12094</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>553</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>4</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-130734</v>
+      </c>
+      <c r="F96" t="n">
+        <v>12094</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>3521869</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>PRADO GARCIA EDISON DANIEL - 1053329911 - 12095</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>510</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>56</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3345952</v>
+      </c>
+      <c r="F101" t="n">
+        <v>12095</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>511</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>56</v>
+      </c>
+      <c r="E102" t="n">
+        <v>464978</v>
+      </c>
+      <c r="F102" t="n">
+        <v>12095</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>520</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1324867</v>
+      </c>
+      <c r="F103" t="n">
+        <v>12095</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>552</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F104" t="n">
+        <v>12095</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>553</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F105" t="n">
+        <v>12095</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>4868121</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>CERINZA RODRIGUEZ NICOLAS ANTONIO - 1072668473 - 12096</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>510</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>56</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3345952</v>
+      </c>
+      <c r="F110" t="n">
+        <v>12096</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>511</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>56</v>
+      </c>
+      <c r="E111" t="n">
+        <v>464978</v>
+      </c>
+      <c r="F111" t="n">
+        <v>12096</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>520</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1324867</v>
+      </c>
+      <c r="F112" t="n">
+        <v>12096</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>552</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F113" t="n">
+        <v>12096</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>553</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F114" t="n">
+        <v>12096</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>4868121</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>GUERRERO BONILLA MICHEL ANDREA - 1000810218 - 12097</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>510</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>55</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3209993</v>
+      </c>
+      <c r="F119" t="n">
+        <v>12097</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>511</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>55</v>
+      </c>
+      <c r="E120" t="n">
+        <v>456675</v>
+      </c>
+      <c r="F120" t="n">
+        <v>12097</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>520</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>448000</v>
+      </c>
+      <c r="F121" t="n">
+        <v>12097</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>552</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-128399</v>
+      </c>
+      <c r="F122" t="n">
+        <v>12097</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>553</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-128399</v>
+      </c>
+      <c r="F123" t="n">
+        <v>12097</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3857870</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>JIMENEZ MORENO LEIDY KATHERINE - 1030616451 - 12098</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>510</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>55</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3209993</v>
+      </c>
+      <c r="F128" t="n">
+        <v>12098</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>511</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>55</v>
+      </c>
+      <c r="E129" t="n">
+        <v>456675</v>
+      </c>
+      <c r="F129" t="n">
+        <v>12098</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>520</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>158333</v>
+      </c>
+      <c r="F130" t="n">
+        <v>12098</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>552</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="n">
+        <v>-130734</v>
+      </c>
+      <c r="F131" t="n">
+        <v>12098</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>553</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-130734</v>
+      </c>
+      <c r="F132" t="n">
+        <v>12098</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>3563533</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>DIAZ ORTEGA JORGE ARMANDO - 1143264961 - 12103</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>510</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>53</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3142361</v>
+      </c>
+      <c r="F137" t="n">
+        <v>12103</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>511</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>53</v>
+      </c>
+      <c r="E138" t="n">
+        <v>440069</v>
+      </c>
+      <c r="F138" t="n">
+        <v>12103</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>520</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="F139" t="n">
+        <v>12103</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>552</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-125694</v>
+      </c>
+      <c r="F140" t="n">
+        <v>12103</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>553</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>4</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-125694</v>
+      </c>
+      <c r="F141" t="n">
+        <v>12103</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>4706042</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>BELTRAN CAMACHO NILSSON - 5874263 - 12104</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>510</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>52</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3163998</v>
+      </c>
+      <c r="F146" t="n">
+        <v>12104</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>511</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>52</v>
+      </c>
+      <c r="E147" t="n">
+        <v>431765</v>
+      </c>
+      <c r="F147" t="n">
+        <v>12104</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>520</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1408060</v>
+      </c>
+      <c r="F148" t="n">
+        <v>12104</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>552</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>3</v>
+      </c>
+      <c r="E149" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F149" t="n">
+        <v>12104</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>553</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>3</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F150" t="n">
+        <v>12104</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>4750703</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>VERGARA ZUBIETA CARLOS ALBERTO - 14273010 - 12105</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>510</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>52</v>
+      </c>
+      <c r="E155" t="n">
+        <v>3083998</v>
+      </c>
+      <c r="F155" t="n">
+        <v>12105</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>511</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>52</v>
+      </c>
+      <c r="E156" t="n">
+        <v>431765</v>
+      </c>
+      <c r="F156" t="n">
+        <v>12105</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>520</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>690667</v>
+      </c>
+      <c r="F157" t="n">
+        <v>12105</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>552</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>3</v>
+      </c>
+      <c r="E158" t="n">
+        <v>-123360</v>
+      </c>
+      <c r="F158" t="n">
+        <v>12105</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>553</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>3</v>
+      </c>
+      <c r="E159" t="n">
+        <v>-123360</v>
+      </c>
+      <c r="F159" t="n">
+        <v>12105</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>3959710</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>VIZCAYA GARZON LUIS ALEXANDER - 79470821 - 12106</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>510</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>52</v>
+      </c>
+      <c r="E164" t="n">
+        <v>3163998</v>
+      </c>
+      <c r="F164" t="n">
+        <v>12106</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>511</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>52</v>
+      </c>
+      <c r="E165" t="n">
+        <v>431765</v>
+      </c>
+      <c r="F165" t="n">
+        <v>12106</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>520</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1408060</v>
+      </c>
+      <c r="F166" t="n">
+        <v>12106</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>552</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>3</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F167" t="n">
+        <v>12106</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>553</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>3</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F168" t="n">
+        <v>12106</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>4750703</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>BELTRAN BOCACHICA JUAN CARLOS - 79697019 - 12107</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>510</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>52</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3163998</v>
+      </c>
+      <c r="F173" t="n">
+        <v>12107</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>511</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>52</v>
+      </c>
+      <c r="E174" t="n">
+        <v>431765</v>
+      </c>
+      <c r="F174" t="n">
+        <v>12107</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>520</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1408060</v>
+      </c>
+      <c r="F175" t="n">
+        <v>12107</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>552</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>3</v>
+      </c>
+      <c r="E176" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F176" t="n">
+        <v>12107</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>553</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>3</v>
+      </c>
+      <c r="E177" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F177" t="n">
+        <v>12107</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>4750703</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>GARCIA MARTINEZ HEROL - 1005220326 - 12108</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>510</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>52</v>
+      </c>
+      <c r="E182" t="n">
+        <v>3163998</v>
+      </c>
+      <c r="F182" t="n">
+        <v>12108</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>511</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>52</v>
+      </c>
+      <c r="E183" t="n">
+        <v>431766</v>
+      </c>
+      <c r="F183" t="n">
+        <v>12108</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>520</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="F184" t="n">
+        <v>12108</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>552</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>4</v>
+      </c>
+      <c r="E185" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F185" t="n">
+        <v>12108</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>553</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>4</v>
+      </c>
+      <c r="E186" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F186" t="n">
+        <v>12108</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>5582644</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>CHAPARRO COBOS VALENTINA - 1010005789 - 12109</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>510</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>52</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3083998</v>
+      </c>
+      <c r="F191" t="n">
+        <v>12109</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>511</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>52</v>
+      </c>
+      <c r="E192" t="n">
+        <v>431765</v>
+      </c>
+      <c r="F192" t="n">
+        <v>12109</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>520</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>690667</v>
+      </c>
+      <c r="F193" t="n">
+        <v>12109</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>552</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>3</v>
+      </c>
+      <c r="E194" t="n">
+        <v>-123360</v>
+      </c>
+      <c r="F194" t="n">
+        <v>12109</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>553</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>3</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-123360</v>
+      </c>
+      <c r="F195" t="n">
+        <v>12109</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>3959710</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>VIZCAYA CASTAÑO JEIMY NATALIA - 1013685026 - 12110</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>510</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>52</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3034903</v>
+      </c>
+      <c r="F200" t="n">
+        <v>12110</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>511</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>52</v>
+      </c>
+      <c r="E201" t="n">
+        <v>431765</v>
+      </c>
+      <c r="F201" t="n">
+        <v>12110</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>520</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>414400</v>
+      </c>
+      <c r="F202" t="n">
+        <v>12110</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>552</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>3</v>
+      </c>
+      <c r="E203" t="n">
+        <v>-121396</v>
+      </c>
+      <c r="F203" t="n">
+        <v>12110</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>553</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>3</v>
+      </c>
+      <c r="E204" t="n">
+        <v>-121396</v>
+      </c>
+      <c r="F204" t="n">
+        <v>12110</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>3638276</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>ROJAS BELTRAN ALCIDES - 1019018752 - 12111</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>510</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>52</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3163998</v>
+      </c>
+      <c r="F209" t="n">
+        <v>12111</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>511</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>52</v>
+      </c>
+      <c r="E210" t="n">
+        <v>431765</v>
+      </c>
+      <c r="F210" t="n">
+        <v>12111</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>520</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1408060</v>
+      </c>
+      <c r="F211" t="n">
+        <v>12111</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>552</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>3</v>
+      </c>
+      <c r="E212" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F212" t="n">
+        <v>12111</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>553</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>3</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F213" t="n">
+        <v>12111</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>4750703</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>RIVERA CHILA YESICA YULIETH - 1031133915 - 12112</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>510</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>52</v>
+      </c>
+      <c r="E218" t="n">
+        <v>3163998</v>
+      </c>
+      <c r="F218" t="n">
+        <v>12112</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>511</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>52</v>
+      </c>
+      <c r="E219" t="n">
+        <v>431765</v>
+      </c>
+      <c r="F219" t="n">
+        <v>12112</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>520</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1408060</v>
+      </c>
+      <c r="F220" t="n">
+        <v>12112</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>552</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>3</v>
+      </c>
+      <c r="E221" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F221" t="n">
+        <v>12112</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>553</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>3</v>
+      </c>
+      <c r="E222" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F222" t="n">
+        <v>12112</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>4750703</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>SILVA OTRIZ HERNAN GABRIEL - 1095815439 - 12113</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>510</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>52</v>
+      </c>
+      <c r="E227" t="n">
+        <v>3163998</v>
+      </c>
+      <c r="F227" t="n">
+        <v>12113</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>511</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>52</v>
+      </c>
+      <c r="E228" t="n">
+        <v>431766</v>
+      </c>
+      <c r="F228" t="n">
+        <v>12113</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>520</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1522667</v>
+      </c>
+      <c r="F229" t="n">
+        <v>12113</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>552</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>4</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F230" t="n">
+        <v>12113</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>553</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>4</v>
+      </c>
+      <c r="E231" t="n">
+        <v>-126560</v>
+      </c>
+      <c r="F231" t="n">
+        <v>12113</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>4865311</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>ACOSTA AYOLA SANTIAGO ALFONSO - 1030676580 - 12073</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>510</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>32</v>
+      </c>
+      <c r="E236" t="n">
+        <v>2666667</v>
+      </c>
+      <c r="F236" t="n">
+        <v>12073</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>511</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>32</v>
+      </c>
+      <c r="E237" t="n">
+        <v>265701</v>
+      </c>
+      <c r="F237" t="n">
+        <v>12073</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>520</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>286200</v>
+      </c>
+      <c r="F238" t="n">
+        <v>12073</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>552</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>2</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-106667</v>
+      </c>
+      <c r="F239" t="n">
+        <v>12073</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>553</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>2</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-106667</v>
+      </c>
+      <c r="F240" t="n">
+        <v>12073</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>3005234</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>LOPEZ JAIMES LEIDY KATHERINE - 1098749160 - 12114</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>510</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>52</v>
+      </c>
+      <c r="E245" t="n">
+        <v>3183998</v>
+      </c>
+      <c r="F245" t="n">
+        <v>12114</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>511</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>52</v>
+      </c>
+      <c r="E246" t="n">
+        <v>431766</v>
+      </c>
+      <c r="F246" t="n">
+        <v>12114</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>520</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>900000</v>
+      </c>
+      <c r="F247" t="n">
+        <v>12114</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>552</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>4</v>
+      </c>
+      <c r="E248" t="n">
+        <v>-127360</v>
+      </c>
+      <c r="F248" t="n">
+        <v>12114</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>553</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>4</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-127360</v>
+      </c>
+      <c r="F249" t="n">
+        <v>12114</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>4261044</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>PINTO GALEANO KAREN DAYANNA - 1193587681 - 12115</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>510</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>52</v>
+      </c>
+      <c r="E254" t="n">
+        <v>3034904</v>
+      </c>
+      <c r="F254" t="n">
+        <v>12115</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>511</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>52</v>
+      </c>
+      <c r="E255" t="n">
+        <v>431766</v>
+      </c>
+      <c r="F255" t="n">
+        <v>12115</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>520</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F256" t="n">
+        <v>12115</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>552</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>4</v>
+      </c>
+      <c r="E257" t="n">
+        <v>-121396</v>
+      </c>
+      <c r="F257" t="n">
+        <v>12115</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>553</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>4</v>
+      </c>
+      <c r="E258" t="n">
+        <v>-121396</v>
+      </c>
+      <c r="F258" t="n">
+        <v>12115</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>3523878</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>GALINDO TORRES WILSON - 4138293 - 12116</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D262" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>510</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>47</v>
+      </c>
+      <c r="E263" t="n">
+        <v>2872180</v>
+      </c>
+      <c r="F263" t="n">
+        <v>12116</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>511</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>47</v>
+      </c>
+      <c r="E264" t="n">
+        <v>390249</v>
+      </c>
+      <c r="F264" t="n">
+        <v>12116</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>520</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1261140</v>
+      </c>
+      <c r="F265" t="n">
+        <v>12116</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>530</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Licencia NO Remunerada</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" t="n">
+        <v>58363</v>
+      </c>
+      <c r="F266" t="n">
+        <v>12116</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>552</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" t="n">
+        <v>-114888</v>
+      </c>
+      <c r="F267" t="n">
+        <v>12116</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>553</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>3</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-114888</v>
+      </c>
+      <c r="F268" t="n">
+        <v>12116</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>555</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Licencia NO Remunerada</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" t="n">
+        <v>-58363</v>
+      </c>
+      <c r="F269" t="n">
+        <v>12116</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>4293793</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>VALERO RODRIGUEZ KAREN JOHANNA - 1233511167 - 12117</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>510</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>48</v>
+      </c>
+      <c r="E274" t="n">
+        <v>3276600</v>
+      </c>
+      <c r="F274" t="n">
+        <v>12117</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>511</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>48</v>
+      </c>
+      <c r="E275" t="n">
+        <v>398553</v>
+      </c>
+      <c r="F275" t="n">
+        <v>12117</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>520</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>696200</v>
+      </c>
+      <c r="F276" t="n">
+        <v>12117</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>552</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>3</v>
+      </c>
+      <c r="E277" t="n">
+        <v>-131064</v>
+      </c>
+      <c r="F277" t="n">
+        <v>12117</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>553</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>3</v>
+      </c>
+      <c r="E278" t="n">
+        <v>-131064</v>
+      </c>
+      <c r="F278" t="n">
+        <v>12117</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>4109225</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>MARTINEZ VELASQUEZ MICHAEL STEVEN - 1012399538 - 11647</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>510</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>60</v>
+      </c>
+      <c r="E283" t="n">
+        <v>3501811</v>
+      </c>
+      <c r="F283" t="n">
+        <v>11647</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>511</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>60</v>
+      </c>
+      <c r="E284" t="n">
+        <v>498191</v>
+      </c>
+      <c r="F284" t="n">
+        <v>11647</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>520</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>315000</v>
+      </c>
+      <c r="F285" t="n">
+        <v>11647</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>524</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Intereses de Cesantias</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>20</v>
+      </c>
+      <c r="E286" t="n">
+        <v>601</v>
+      </c>
+      <c r="F286" t="n">
+        <v>11647</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>552</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>3</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-140072</v>
+      </c>
+      <c r="F287" t="n">
+        <v>11647</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>553</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>3</v>
+      </c>
+      <c r="E288" t="n">
+        <v>-140072</v>
+      </c>
+      <c r="F288" t="n">
+        <v>11647</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>4035459</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>YARA PULIDO DAVID FERNANDO - 1018490950 - 11648</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D292" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>510</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>60</v>
+      </c>
+      <c r="E293" t="n">
+        <v>3586175</v>
+      </c>
+      <c r="F293" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>511</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>60</v>
+      </c>
+      <c r="E294" t="n">
+        <v>498191</v>
+      </c>
+      <c r="F294" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>520</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>515000</v>
+      </c>
+      <c r="F295" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>524</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Intereses de Cesantias</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>20</v>
+      </c>
+      <c r="E296" t="n">
+        <v>676</v>
+      </c>
+      <c r="F296" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>552</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>3</v>
+      </c>
+      <c r="E297" t="n">
+        <v>-143447</v>
+      </c>
+      <c r="F297" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>553</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>3</v>
+      </c>
+      <c r="E298" t="n">
+        <v>-143447</v>
+      </c>
+      <c r="F298" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>4313148</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>LOPEZ ROBLES EDWIN ANTONIO - 7186392 - 12086</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>510</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>56</v>
+      </c>
+      <c r="E303" t="n">
+        <v>3345952</v>
+      </c>
+      <c r="F303" t="n">
+        <v>12086</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>511</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>56</v>
+      </c>
+      <c r="E304" t="n">
+        <v>464978</v>
+      </c>
+      <c r="F304" t="n">
+        <v>12086</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>520</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1324867</v>
+      </c>
+      <c r="F305" t="n">
+        <v>12086</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>552</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>3</v>
+      </c>
+      <c r="E306" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F306" t="n">
+        <v>12086</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>553</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>3</v>
+      </c>
+      <c r="E307" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F307" t="n">
+        <v>12086</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>4868121</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>RIVERA OVIEDO ANDRES HEBERTO - 1004211263 - 12100</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>510</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>53</v>
+      </c>
+      <c r="E312" t="n">
+        <v>3331533</v>
+      </c>
+      <c r="F312" t="n">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>511</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>53</v>
+      </c>
+      <c r="E313" t="n">
+        <v>440069</v>
+      </c>
+      <c r="F313" t="n">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>520</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F314" t="n">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>552</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>4</v>
+      </c>
+      <c r="E315" t="n">
+        <v>-133261</v>
+      </c>
+      <c r="F315" t="n">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>553</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>4</v>
+      </c>
+      <c r="E316" t="n">
+        <v>-133261</v>
+      </c>
+      <c r="F316" t="n">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>4305080</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>QUIÑONEZ BAYONA STEFANNY LISETH - 1007582396 - 12101</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E320" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>510</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>53</v>
+      </c>
+      <c r="E321" t="n">
+        <v>3093267</v>
+      </c>
+      <c r="F321" t="n">
+        <v>12101</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>511</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>53</v>
+      </c>
+      <c r="E322" t="n">
+        <v>440069</v>
+      </c>
+      <c r="F322" t="n">
+        <v>12101</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>520</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F323" t="n">
+        <v>12101</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>552</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>4</v>
+      </c>
+      <c r="E324" t="n">
+        <v>-123730</v>
+      </c>
+      <c r="F324" t="n">
+        <v>12101</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>553</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>4</v>
+      </c>
+      <c r="E325" t="n">
+        <v>-123730</v>
+      </c>
+      <c r="F325" t="n">
+        <v>12101</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>3585876</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>OROZCO HERRERA WANNER LUIS - 1067719339 - 12102</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E329" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>510</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>53</v>
+      </c>
+      <c r="E330" t="n">
+        <v>3142361</v>
+      </c>
+      <c r="F330" t="n">
+        <v>12102</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>511</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>53</v>
+      </c>
+      <c r="E331" t="n">
+        <v>440069</v>
+      </c>
+      <c r="F331" t="n">
+        <v>12102</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>520</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1512000</v>
+      </c>
+      <c r="F332" t="n">
+        <v>12102</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>552</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>4</v>
+      </c>
+      <c r="E333" t="n">
+        <v>-125694</v>
+      </c>
+      <c r="F333" t="n">
+        <v>12102</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>553</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>4</v>
+      </c>
+      <c r="E334" t="n">
+        <v>-125694</v>
+      </c>
+      <c r="F334" t="n">
+        <v>12102</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>4843042</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>TAUTIVA SOLORZANO JESUS OCTAVIO - 86058644 - 12118</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E338" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>510</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>47</v>
+      </c>
+      <c r="E339" t="n">
+        <v>2872180</v>
+      </c>
+      <c r="F339" t="n">
+        <v>12118</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>511</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>47</v>
+      </c>
+      <c r="E340" t="n">
+        <v>390249</v>
+      </c>
+      <c r="F340" t="n">
+        <v>12118</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>520</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1224410</v>
+      </c>
+      <c r="F341" t="n">
+        <v>12118</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>552</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>3</v>
+      </c>
+      <c r="E342" t="n">
+        <v>-114887</v>
+      </c>
+      <c r="F342" t="n">
+        <v>12118</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>553</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>3</v>
+      </c>
+      <c r="E343" t="n">
+        <v>-114887</v>
+      </c>
+      <c r="F343" t="n">
+        <v>12118</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>4257065</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="inlineStr">
+        <is>
+          <t>GONZALEZ PEÑA JAVIER RICARDO - 1014193668 - 12119</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D347" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E347" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>510</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>47</v>
+      </c>
+      <c r="E348" t="n">
+        <v>2872180</v>
+      </c>
+      <c r="F348" t="n">
+        <v>12119</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>511</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>47</v>
+      </c>
+      <c r="E349" t="n">
+        <v>390249</v>
+      </c>
+      <c r="F349" t="n">
+        <v>12119</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>520</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1224410</v>
+      </c>
+      <c r="F350" t="n">
+        <v>12119</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>552</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>3</v>
+      </c>
+      <c r="E351" t="n">
+        <v>-114887</v>
+      </c>
+      <c r="F351" t="n">
+        <v>12119</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>553</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>3</v>
+      </c>
+      <c r="E352" t="n">
+        <v>-114887</v>
+      </c>
+      <c r="F352" t="n">
+        <v>12119</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>4257065</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>GALVIS BARRETO ROBER ELIAS - 1098715090 - 12077</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E356" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>510</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>59</v>
+      </c>
+      <c r="E357" t="n">
+        <v>3592542</v>
+      </c>
+      <c r="F357" t="n">
+        <v>12077</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>511</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>59</v>
+      </c>
+      <c r="E358" t="n">
+        <v>489888</v>
+      </c>
+      <c r="F358" t="n">
+        <v>12077</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>520</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>900000</v>
+      </c>
+      <c r="F359" t="n">
+        <v>12077</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>552</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>4</v>
+      </c>
+      <c r="E360" t="n">
+        <v>-143702</v>
+      </c>
+      <c r="F360" t="n">
+        <v>12077</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="n">
+        <v>553</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>4</v>
+      </c>
+      <c r="E361" t="n">
+        <v>-143702</v>
+      </c>
+      <c r="F361" t="n">
+        <v>12077</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>4695026</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C364" s="3" t="inlineStr">
+        <is>
+          <t>SANCHEZ SILVA ARIEL - 18955643 - 12078</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E365" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="n">
+        <v>510</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>59</v>
+      </c>
+      <c r="E366" t="n">
+        <v>3492542</v>
+      </c>
+      <c r="F366" t="n">
+        <v>12078</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="n">
+        <v>511</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>59</v>
+      </c>
+      <c r="E367" t="n">
+        <v>489888</v>
+      </c>
+      <c r="F367" t="n">
+        <v>12078</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="n">
+        <v>520</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" t="n">
+        <v>1481667</v>
+      </c>
+      <c r="F368" t="n">
+        <v>12078</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>552</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>4</v>
+      </c>
+      <c r="E369" t="n">
+        <v>-139702</v>
+      </c>
+      <c r="F369" t="n">
+        <v>12078</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>553</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>4</v>
+      </c>
+      <c r="E370" t="n">
+        <v>-139702</v>
+      </c>
+      <c r="F370" t="n">
+        <v>12078</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>5184693</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="inlineStr">
+        <is>
+          <t>GRANADOS AVELLANEDA JOSE FRANCISCO - 1096234285 - 12120</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C374" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E374" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>510</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>20</v>
+      </c>
+      <c r="E375" t="n">
+        <v>1253333</v>
+      </c>
+      <c r="F375" t="n">
+        <v>12120</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>511</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>20</v>
+      </c>
+      <c r="E376" t="n">
+        <v>166064</v>
+      </c>
+      <c r="F376" t="n">
+        <v>12120</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>520</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>0</v>
+      </c>
+      <c r="E377" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F377" t="n">
+        <v>12120</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>552</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>2</v>
+      </c>
+      <c r="E378" t="n">
+        <v>-50133</v>
+      </c>
+      <c r="F378" t="n">
+        <v>12120</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>553</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>2</v>
+      </c>
+      <c r="E379" t="n">
+        <v>-50133</v>
+      </c>
+      <c r="F379" t="n">
+        <v>12120</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>2119131</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C382" s="3" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ CACERES CRISTIAN CAMILO - 1066084519 - 12121</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E383" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>510</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>15</v>
+      </c>
+      <c r="E384" t="n">
+        <v>900000</v>
+      </c>
+      <c r="F384" t="n">
+        <v>12121</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>511</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>15</v>
+      </c>
+      <c r="E385" t="n">
+        <v>124548</v>
+      </c>
+      <c r="F385" t="n">
+        <v>12121</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>552</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>1</v>
+      </c>
+      <c r="E386" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="F386" t="n">
+        <v>12121</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>553</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>1</v>
+      </c>
+      <c r="E387" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="F387" t="n">
+        <v>12121</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>952548</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C390" s="3" t="inlineStr">
+        <is>
+          <t>GARCIA RODRIGUEZ LIUVA YANIN - 1094165897 - 11646</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C391" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D391" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E391" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="n">
+        <v>510</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>60</v>
+      </c>
+      <c r="E392" t="n">
+        <v>4289820</v>
+      </c>
+      <c r="F392" t="n">
+        <v>11646</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="n">
+        <v>511</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>60</v>
+      </c>
+      <c r="E393" t="n">
+        <v>498191</v>
+      </c>
+      <c r="F393" t="n">
+        <v>11646</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="n">
+        <v>520</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="F394" t="n">
+        <v>11646</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="n">
+        <v>524</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Intereses de Cesantias</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>20</v>
+      </c>
+      <c r="E395" t="n">
+        <v>820</v>
+      </c>
+      <c r="F395" t="n">
+        <v>11646</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="n">
+        <v>552</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>3</v>
+      </c>
+      <c r="E396" t="n">
+        <v>-171593</v>
+      </c>
+      <c r="F396" t="n">
+        <v>11646</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="n">
+        <v>553</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>3</v>
+      </c>
+      <c r="E397" t="n">
+        <v>-171593</v>
+      </c>
+      <c r="F397" t="n">
+        <v>11646</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>5845645</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C400" s="3" t="inlineStr">
+        <is>
+          <t>HERNANDEZ BARERO HASBLEIDY ALEXANDRA - 1018487668 - 12074</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C401" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="n">
+        <v>510</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>59</v>
+      </c>
+      <c r="E402" t="n">
+        <v>3519948</v>
+      </c>
+      <c r="F402" t="n">
+        <v>12074</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="n">
+        <v>511</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>59</v>
+      </c>
+      <c r="E403" t="n">
+        <v>489888</v>
+      </c>
+      <c r="F403" t="n">
+        <v>12074</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="n">
+        <v>520</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F404" t="n">
+        <v>12074</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="n">
+        <v>524</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Intereses de Cesantias</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>2</v>
+      </c>
+      <c r="E405" t="n">
+        <v>6</v>
+      </c>
+      <c r="F405" t="n">
+        <v>12074</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="n">
+        <v>530</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Licencia NO Remunerada</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>1</v>
+      </c>
+      <c r="E406" t="n">
+        <v>58363</v>
+      </c>
+      <c r="F406" t="n">
+        <v>12074</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="n">
+        <v>552</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>4</v>
+      </c>
+      <c r="E407" t="n">
+        <v>-140798</v>
+      </c>
+      <c r="F407" t="n">
+        <v>12074</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="n">
+        <v>553</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>4</v>
+      </c>
+      <c r="E408" t="n">
+        <v>-140798</v>
+      </c>
+      <c r="F408" t="n">
+        <v>12074</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="n">
+        <v>555</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Licencia NO Remunerada</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>1</v>
+      </c>
+      <c r="E409" t="n">
+        <v>-58363</v>
+      </c>
+      <c r="F409" t="n">
+        <v>12074</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>4178246</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C412" s="3" t="inlineStr">
+        <is>
+          <t>PRECIADO GUERRERO WILLIAM - 79825475 - 12075</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D413" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E413" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="n">
+        <v>510</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>60</v>
+      </c>
+      <c r="E414" t="n">
+        <v>3683312</v>
+      </c>
+      <c r="F414" t="n">
+        <v>12075</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="n">
+        <v>511</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>60</v>
+      </c>
+      <c r="E415" t="n">
+        <v>498192</v>
+      </c>
+      <c r="F415" t="n">
+        <v>12075</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="n">
+        <v>520</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>2380000</v>
+      </c>
+      <c r="F416" t="n">
+        <v>12075</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="n">
+        <v>524</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Intereses de Cesantias</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>2</v>
+      </c>
+      <c r="E417" t="n">
+        <v>7</v>
+      </c>
+      <c r="F417" t="n">
+        <v>12075</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="n">
+        <v>552</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>4</v>
+      </c>
+      <c r="E418" t="n">
+        <v>-147332</v>
+      </c>
+      <c r="F418" t="n">
+        <v>12075</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="n">
+        <v>553</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>4</v>
+      </c>
+      <c r="E419" t="n">
+        <v>-147332</v>
+      </c>
+      <c r="F419" t="n">
+        <v>12075</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>6266847</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="inlineStr">
+        <is>
+          <t>CAPACHO HERNANDEZ MAYRA ALEJANDRA - 1095929305 - 12076</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C423" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D423" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E423" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="n">
+        <v>510</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>59</v>
+      </c>
+      <c r="E424" t="n">
+        <v>3708367</v>
+      </c>
+      <c r="F424" t="n">
+        <v>12076</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="n">
+        <v>511</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>59</v>
+      </c>
+      <c r="E425" t="n">
+        <v>489888</v>
+      </c>
+      <c r="F425" t="n">
+        <v>12076</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="n">
+        <v>520</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="F426" t="n">
+        <v>12076</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="n">
+        <v>552</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>4</v>
+      </c>
+      <c r="E427" t="n">
+        <v>-148335</v>
+      </c>
+      <c r="F427" t="n">
+        <v>12076</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="n">
+        <v>553</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>4</v>
+      </c>
+      <c r="E428" t="n">
+        <v>-148335</v>
+      </c>
+      <c r="F428" t="n">
+        <v>12076</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>5601585</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="inlineStr">
+        <is>
+          <t>LIZARAZO ORDONEZ YERSON FERLEY - 1098731565 - 12085</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C432" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D432" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E432" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="n">
+        <v>510</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>59</v>
+      </c>
+      <c r="E433" t="n">
+        <v>3572542</v>
+      </c>
+      <c r="F433" t="n">
+        <v>12085</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="n">
+        <v>511</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>59</v>
+      </c>
+      <c r="E434" t="n">
+        <v>489888</v>
+      </c>
+      <c r="F434" t="n">
+        <v>12085</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="n">
+        <v>520</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="n">
+        <v>1660333</v>
+      </c>
+      <c r="F435" t="n">
+        <v>12085</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="n">
+        <v>552</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>4</v>
+      </c>
+      <c r="E436" t="n">
+        <v>-142902</v>
+      </c>
+      <c r="F436" t="n">
+        <v>12085</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="n">
+        <v>553</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>4</v>
+      </c>
+      <c r="E437" t="n">
+        <v>-142902</v>
+      </c>
+      <c r="F437" t="n">
+        <v>12085</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>5436959</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="inlineStr">
+        <is>
+          <t>SOLINA RODRIGUEZ JOSE LUIS - 79892593 - 12092</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C441" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D441" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E441" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" t="n">
+        <v>510</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>56</v>
+      </c>
+      <c r="E442" t="n">
+        <v>3345952</v>
+      </c>
+      <c r="F442" t="n">
+        <v>12092</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" t="n">
+        <v>511</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>56</v>
+      </c>
+      <c r="E443" t="n">
+        <v>464977</v>
+      </c>
+      <c r="F443" t="n">
+        <v>12092</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" t="n">
+        <v>520</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>0</v>
+      </c>
+      <c r="E444" t="n">
+        <v>1324867</v>
+      </c>
+      <c r="F444" t="n">
+        <v>12092</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" t="n">
+        <v>552</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>3</v>
+      </c>
+      <c r="E445" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F445" t="n">
+        <v>12092</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" t="n">
+        <v>553</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>3</v>
+      </c>
+      <c r="E446" t="n">
+        <v>-133838</v>
+      </c>
+      <c r="F446" t="n">
+        <v>12092</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>4868120</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C449" s="3" t="inlineStr">
+        <is>
+          <t>CAVIEDES CRISTANCHO LILIANA PATRICIA - 37862695 - 12099</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C450" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D450" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E450" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" t="n">
+        <v>510</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>53</v>
+      </c>
+      <c r="E451" t="n">
+        <v>3192361</v>
+      </c>
+      <c r="F451" t="n">
+        <v>12099</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" t="n">
+        <v>511</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>53</v>
+      </c>
+      <c r="E452" t="n">
+        <v>440069</v>
+      </c>
+      <c r="F452" t="n">
+        <v>12099</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" t="n">
+        <v>520</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>0</v>
+      </c>
+      <c r="E453" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="F453" t="n">
+        <v>12099</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" t="n">
+        <v>552</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>4</v>
+      </c>
+      <c r="E454" t="n">
+        <v>-127694</v>
+      </c>
+      <c r="F454" t="n">
+        <v>12099</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" t="n">
+        <v>553</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>4</v>
+      </c>
+      <c r="E455" t="n">
+        <v>-127694</v>
+      </c>
+      <c r="F455" t="n">
+        <v>12099</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>4977042</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>NAVARRO MUÑOZ DANIEL JOSE - 1007317314 - 12082</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C459" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D459" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E459" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" t="n">
+        <v>510</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>29</v>
+      </c>
+      <c r="E460" t="n">
+        <v>1692542</v>
+      </c>
+      <c r="F460" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" t="n">
+        <v>511</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>29</v>
+      </c>
+      <c r="E461" t="n">
+        <v>240791</v>
+      </c>
+      <c r="F461" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" t="n">
+        <v>520</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>713334</v>
+      </c>
+      <c r="F462" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" t="n">
+        <v>523</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Cesantias</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>29</v>
+      </c>
+      <c r="E463" t="n">
+        <v>161112</v>
+      </c>
+      <c r="F463" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" t="n">
+        <v>524</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Intereses de Cesantias</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>29</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1612</v>
+      </c>
+      <c r="F464" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" t="n">
+        <v>526</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Prima de Servicios</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>30</v>
+      </c>
+      <c r="E465" t="n">
+        <v>166667</v>
+      </c>
+      <c r="F465" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" t="n">
+        <v>530</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Licencia NO Remunerada</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>1</v>
+      </c>
+      <c r="E466" t="n">
+        <v>58363</v>
+      </c>
+      <c r="F466" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" t="n">
+        <v>534</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Vacaciones Compensadas</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E467" t="n">
+        <v>70620</v>
+      </c>
+      <c r="F467" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" t="n">
+        <v>552</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>3</v>
+      </c>
+      <c r="E468" t="n">
+        <v>-67703</v>
+      </c>
+      <c r="F468" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" t="n">
+        <v>553</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>3</v>
+      </c>
+      <c r="E469" t="n">
+        <v>-67703</v>
+      </c>
+      <c r="F469" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" t="n">
+        <v>555</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Licencia NO Remunerada</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>1</v>
+      </c>
+      <c r="E470" t="n">
+        <v>-58363</v>
+      </c>
+      <c r="F470" t="n">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>2911272</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Empleado</t>
+        </is>
+      </c>
+      <c r="C473" s="3" t="inlineStr">
+        <is>
+          <t>CORREDOR JIMENEZ FREDDY ALONSO - 5416907 - 12079</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" s="4" t="inlineStr">
+        <is>
+          <t>Id Concepto</t>
+        </is>
+      </c>
+      <c r="C474" s="4" t="inlineStr">
+        <is>
+          <t>Nombre Concepto</t>
+        </is>
+      </c>
+      <c r="D474" s="4" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="E474" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" t="n">
+        <v>510</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Sueldo Basico</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>30</v>
+      </c>
+      <c r="E475" t="n">
+        <v>1750906</v>
+      </c>
+      <c r="F475" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" t="n">
+        <v>511</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Auxilio de Transporte</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>30</v>
+      </c>
+      <c r="E476" t="n">
+        <v>249095</v>
+      </c>
+      <c r="F476" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" t="n">
+        <v>520</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Auxilio de Rodamiento</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>0</v>
+      </c>
+      <c r="E477" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F477" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" t="n">
+        <v>523</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Cesantias</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>30</v>
+      </c>
+      <c r="E478" t="n">
+        <v>166667</v>
+      </c>
+      <c r="F478" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" t="n">
+        <v>524</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Intereses de Cesantias</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>30</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1667</v>
+      </c>
+      <c r="F479" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" t="n">
+        <v>526</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Prima de Servicios</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>30</v>
+      </c>
+      <c r="E480" t="n">
+        <v>166667</v>
+      </c>
+      <c r="F480" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" t="n">
+        <v>534</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Vacaciones Compensadas</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E481" t="n">
+        <v>72955</v>
+      </c>
+      <c r="F481" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" t="n">
+        <v>552</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>3</v>
+      </c>
+      <c r="E482" t="n">
+        <v>-70037</v>
+      </c>
+      <c r="F482" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" t="n">
+        <v>553</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>AFP</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>3</v>
+      </c>
+      <c r="E483" t="n">
+        <v>-70037</v>
+      </c>
+      <c r="F483" t="n">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>3257883</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C19:H19"/>
+  <mergeCells count="52">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C261:H261"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C117:H117"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="C373:H373"/>
+    <mergeCell ref="C382:H382"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="C301:H301"/>
+    <mergeCell ref="C364:H364"/>
+    <mergeCell ref="C422:H422"/>
+    <mergeCell ref="C291:H291"/>
+    <mergeCell ref="C198:H198"/>
+    <mergeCell ref="C412:H412"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C252:H252"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="C400:H400"/>
+    <mergeCell ref="C207:H207"/>
+    <mergeCell ref="C458:H458"/>
+    <mergeCell ref="C52:H52"/>
+    <mergeCell ref="C61:H61"/>
+    <mergeCell ref="C328:H328"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C272:H272"/>
+    <mergeCell ref="C337:H337"/>
+    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="C153:H153"/>
+    <mergeCell ref="C473:H473"/>
+    <mergeCell ref="C346:H346"/>
     <mergeCell ref="C7:H7"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C72:H72"/>
+    <mergeCell ref="C243:H243"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="C355:H355"/>
+    <mergeCell ref="C189:H189"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C319:H319"/>
+    <mergeCell ref="C390:H390"/>
+    <mergeCell ref="C310:H310"/>
+    <mergeCell ref="C108:H108"/>
+    <mergeCell ref="C431:H431"/>
+    <mergeCell ref="C440:H440"/>
+    <mergeCell ref="C216:H216"/>
+    <mergeCell ref="C449:H449"/>
+    <mergeCell ref="C225:H225"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="C234:H234"/>
+    <mergeCell ref="C281:H281"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C162:H162"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
